--- a/salidas/empresas/ACN.xlsx
+++ b/salidas/empresas/ACN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>21.8549690246582</v>
+        <v>21.85496520996094</v>
       </c>
       <c r="C2" t="n">
         <v>31.53000068664551</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>22.63822555541992</v>
+        <v>22.63822746276855</v>
       </c>
       <c r="C3" t="n">
         <v>32.65999984741211</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>20.84296607971191</v>
+        <v>20.84296798706055</v>
       </c>
       <c r="C4" t="n">
         <v>30.06999969482422</v>
@@ -539,7 +551,7 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
@@ -558,7 +570,7 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>19.62995719909668</v>
+        <v>19.62995910644531</v>
       </c>
       <c r="C7" t="n">
         <v>28.31999969482422</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>20.28151321411133</v>
+        <v>20.28151512145996</v>
       </c>
       <c r="C8" t="n">
         <v>29.26000022888184</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>20.55877685546875</v>
+        <v>20.55877876281738</v>
       </c>
       <c r="C9" t="n">
         <v>29.65999984741211</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>21.97973251342773</v>
+        <v>21.97972869873047</v>
       </c>
       <c r="C10" t="n">
         <v>31.70999908447266</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>23.06472969055176</v>
+        <v>23.06472587585449</v>
       </c>
       <c r="C11" t="n">
         <v>32.90999984741211</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>23.6183967590332</v>
+        <v>23.6184024810791</v>
       </c>
       <c r="C12" t="n">
         <v>33.70000076293945</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>25.88212013244629</v>
+        <v>25.88212203979492</v>
       </c>
       <c r="C13" t="n">
         <v>36.93000030517578</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>26.4568042755127</v>
+        <v>26.45681190490723</v>
       </c>
       <c r="C14" t="n">
         <v>37.75</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>25.07615280151367</v>
+        <v>25.07615089416504</v>
       </c>
       <c r="C15" t="n">
         <v>35.77999877929688</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>27.01047897338867</v>
+        <v>27.01047706604004</v>
       </c>
       <c r="C16" t="n">
         <v>38.54000091552734</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>27.40293121337891</v>
+        <v>27.40295028686523</v>
       </c>
       <c r="C17" t="n">
         <v>39.09999847412109</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>28.6924991607666</v>
+        <v>28.69248962402344</v>
       </c>
       <c r="C18" t="n">
         <v>40.93999862670898</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>30.05913734436035</v>
+        <v>30.05913925170898</v>
       </c>
       <c r="C19" t="n">
         <v>42.88999938964844</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>29.52649879455566</v>
+        <v>29.5264949798584</v>
       </c>
       <c r="C20" t="n">
         <v>42.13000106811523</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>28.8817195892334</v>
+        <v>28.88171195983887</v>
       </c>
       <c r="C21" t="n">
         <v>41.20999908447266</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>28.20891189575195</v>
+        <v>28.20892715454102</v>
       </c>
       <c r="C22" t="n">
         <v>40.25</v>
@@ -881,7 +893,7 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>24.47633743286133</v>
+        <v>24.4763355255127</v>
       </c>
       <c r="C24" t="n">
         <v>34.56000137329102</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>25.51743125915527</v>
+        <v>25.51742744445801</v>
       </c>
       <c r="C25" t="n">
         <v>36.02999877929688</v>
@@ -938,7 +950,7 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>24.96500015258789</v>
+        <v>24.96501922607422</v>
       </c>
       <c r="C27" t="n">
         <v>35.25</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>24.90835189819336</v>
+        <v>24.90836524963379</v>
       </c>
       <c r="C28" t="n">
         <v>35.16999816894531</v>
@@ -995,7 +1007,7 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>28.90982818603516</v>
+        <v>28.90983963012695</v>
       </c>
       <c r="C30" t="n">
         <v>40.81999969482422</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>28.83900833129883</v>
+        <v>28.83901977539062</v>
       </c>
       <c r="C31" t="n">
         <v>40.72000122070312</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>29.57557487487793</v>
+        <v>29.5755672454834</v>
       </c>
       <c r="C32" t="n">
         <v>41.7599983215332</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>29.29228973388672</v>
+        <v>29.29228591918945</v>
       </c>
       <c r="C33" t="n">
         <v>41.36000061035156</v>
@@ -1090,7 +1102,7 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>23.77939796447754</v>
+        <v>23.77938652038574</v>
       </c>
       <c r="C35" t="n">
         <v>33.04999923706055</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>22.29003715515137</v>
+        <v>22.29003524780273</v>
       </c>
       <c r="C36" t="n">
         <v>30.97999954223633</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>23.59232902526855</v>
+        <v>23.59232330322266</v>
       </c>
       <c r="C37" t="n">
         <v>32.79000091552734</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>22.70734405517578</v>
+        <v>22.70734596252441</v>
       </c>
       <c r="C38" t="n">
         <v>31.55999946594238</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>21.00213432312012</v>
+        <v>21.00214004516602</v>
       </c>
       <c r="C39" t="n">
         <v>29.19000053405762</v>
@@ -1204,7 +1216,7 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>21.17481803894043</v>
+        <v>21.1748104095459</v>
       </c>
       <c r="C41" t="n">
         <v>29.43000030517578</v>
@@ -1242,7 +1254,7 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>24.07439422607422</v>
+        <v>24.07439613342285</v>
       </c>
       <c r="C43" t="n">
         <v>33.45999908447266</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>25.23277854919434</v>
+        <v>25.23277282714844</v>
       </c>
       <c r="C44" t="n">
         <v>35.06999969482422</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>23.74341773986816</v>
+        <v>23.74342918395996</v>
       </c>
       <c r="C45" t="n">
         <v>33</v>
@@ -1318,11 +1330,11 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>26.81567192077637</v>
+        <v>26.81567573547363</v>
       </c>
       <c r="C46" t="n">
         <v>37.27000045776367</v>
@@ -1337,11 +1349,11 @@
       <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>27.1964111328125</v>
+        <v>27.19640350341797</v>
       </c>
       <c r="C47" t="n">
         <v>37.08000183105469</v>
@@ -1356,11 +1368,11 @@
       <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>30.10088920593262</v>
+        <v>30.10088729858398</v>
       </c>
       <c r="C48" t="n">
         <v>41.04000091552734</v>
@@ -1375,7 +1387,7 @@
       <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
@@ -1400,11 +1412,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>30.06420707702637</v>
+        <v>30.06420516967773</v>
       </c>
       <c r="C50" t="n">
         <v>40.9900016784668</v>
@@ -1425,11 +1437,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>29.31608200073242</v>
+        <v>29.31608963012695</v>
       </c>
       <c r="C51" t="n">
         <v>39.97000122070312</v>
@@ -1450,11 +1462,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>30.76832008361816</v>
+        <v>30.7683219909668</v>
       </c>
       <c r="C52" t="n">
         <v>41.95000076293945</v>
@@ -1475,7 +1487,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
@@ -1500,11 +1512,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>27.76066589355469</v>
+        <v>27.76067161560059</v>
       </c>
       <c r="C54" t="n">
         <v>37.52000045776367</v>
@@ -1525,11 +1537,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>28.59673881530762</v>
+        <v>28.59673500061035</v>
       </c>
       <c r="C55" t="n">
         <v>38.65000152587891</v>
@@ -1550,11 +1562,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>29.32922744750977</v>
+        <v>29.3292179107666</v>
       </c>
       <c r="C56" t="n">
         <v>39.63999938964844</v>
@@ -1575,11 +1587,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>27.0799617767334</v>
+        <v>27.07996559143066</v>
       </c>
       <c r="C57" t="n">
         <v>36.59999847412109</v>
@@ -1600,11 +1612,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>31.43791580200195</v>
+        <v>31.43791770935059</v>
       </c>
       <c r="C58" t="n">
         <v>42.4900016784668</v>
@@ -1625,11 +1637,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>33.40922164916992</v>
+        <v>33.40922927856445</v>
       </c>
       <c r="C59" t="n">
         <v>44.70999908447266</v>
@@ -1654,11 +1666,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>32.37056350708008</v>
+        <v>32.37055969238281</v>
       </c>
       <c r="C60" t="n">
         <v>43.31999969482422</v>
@@ -1683,11 +1695,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>36.23379516601562</v>
+        <v>36.23379898071289</v>
       </c>
       <c r="C61" t="n">
         <v>48.4900016784668</v>
@@ -1712,11 +1724,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>38.46059036254883</v>
+        <v>38.4605827331543</v>
       </c>
       <c r="C62" t="n">
         <v>51.47000122070312</v>
@@ -1741,11 +1753,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>38.46806335449219</v>
+        <v>38.46805572509766</v>
       </c>
       <c r="C63" t="n">
         <v>51.47999954223633</v>
@@ -1770,11 +1782,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>41.07593536376953</v>
+        <v>41.07594680786133</v>
       </c>
       <c r="C64" t="n">
         <v>54.97000122070312</v>
@@ -1799,11 +1811,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>43.03680038452148</v>
+        <v>43.03680801391602</v>
       </c>
       <c r="C65" t="n">
         <v>57.13000106811523</v>
@@ -1828,11 +1840,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>43.232666015625</v>
+        <v>43.23267364501953</v>
       </c>
       <c r="C66" t="n">
         <v>57.38999938964844</v>
@@ -1857,11 +1869,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>45.51521682739258</v>
+        <v>45.51520538330078</v>
       </c>
       <c r="C67" t="n">
         <v>60.41999816894531</v>
@@ -1886,11 +1898,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>44.55097198486328</v>
+        <v>44.55096054077148</v>
       </c>
       <c r="C68" t="n">
         <v>59.13999938964844</v>
@@ -1915,7 +1927,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
@@ -1944,11 +1956,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>39.6845703125</v>
+        <v>39.6845588684082</v>
       </c>
       <c r="C70" t="n">
         <v>52.68000030517578</v>
@@ -1973,11 +1985,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>45.93849563598633</v>
+        <v>45.93849945068359</v>
       </c>
       <c r="C71" t="n">
         <v>60.2599983215332</v>
@@ -2002,11 +2014,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>44.16225051879883</v>
+        <v>44.16223526000977</v>
       </c>
       <c r="C72" t="n">
         <v>57.93000030517578</v>
@@ -2031,11 +2043,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>40.57926940917969</v>
+        <v>40.57925415039062</v>
       </c>
       <c r="C73" t="n">
         <v>53.22999954223633</v>
@@ -2060,11 +2072,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>43.71247100830078</v>
+        <v>43.71246719360352</v>
       </c>
       <c r="C74" t="n">
         <v>57.34000015258789</v>
@@ -2089,11 +2101,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>45.38961029052734</v>
+        <v>45.38961410522461</v>
       </c>
       <c r="C75" t="n">
         <v>59.54000091552734</v>
@@ -2118,7 +2130,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
@@ -2147,11 +2159,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>50.04882431030273</v>
+        <v>50.048828125</v>
       </c>
       <c r="C77" t="n">
         <v>64.94999694824219</v>
@@ -2176,7 +2188,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
@@ -2205,11 +2217,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>46.3038330078125</v>
+        <v>46.30382537841797</v>
       </c>
       <c r="C79" t="n">
         <v>60.09000015258789</v>
@@ -2234,11 +2246,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>46.46564483642578</v>
+        <v>46.46564865112305</v>
       </c>
       <c r="C80" t="n">
         <v>60.29999923706055</v>
@@ -2263,11 +2275,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>47.4673957824707</v>
+        <v>47.46740341186523</v>
       </c>
       <c r="C81" t="n">
         <v>61.59999847412109</v>
@@ -2292,11 +2304,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>53.96334838867188</v>
+        <v>53.96334457397461</v>
       </c>
       <c r="C82" t="n">
         <v>70.02999877929688</v>
@@ -2321,11 +2333,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>52.54905319213867</v>
+        <v>52.54904937744141</v>
       </c>
       <c r="C83" t="n">
         <v>67.41000366210938</v>
@@ -2350,11 +2362,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>52.94660568237305</v>
+        <v>52.94661712646484</v>
       </c>
       <c r="C84" t="n">
         <v>67.91999816894531</v>
@@ -2379,11 +2391,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>51.83966827392578</v>
+        <v>51.83966445922852</v>
       </c>
       <c r="C85" t="n">
         <v>66.5</v>
@@ -2408,11 +2420,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>56.04141235351562</v>
+        <v>56.04140853881836</v>
       </c>
       <c r="C86" t="n">
         <v>71.88999938964844</v>
@@ -2437,11 +2449,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>57.96688461303711</v>
+        <v>57.96687698364258</v>
       </c>
       <c r="C87" t="n">
         <v>74.36000061035156</v>
@@ -2466,11 +2478,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>59.22194290161133</v>
+        <v>59.22195434570312</v>
       </c>
       <c r="C88" t="n">
         <v>75.97000122070312</v>
@@ -2495,11 +2507,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>64.16806030273438</v>
+        <v>64.16804504394531</v>
       </c>
       <c r="C89" t="n">
         <v>81.44000244140625</v>
@@ -2524,11 +2536,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>64.69598388671875</v>
+        <v>64.69596862792969</v>
       </c>
       <c r="C90" t="n">
         <v>82.11000061035156</v>
@@ -2553,11 +2565,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>56.69860458374023</v>
+        <v>56.6985969543457</v>
       </c>
       <c r="C91" t="n">
         <v>71.95999908447266</v>
@@ -2582,11 +2594,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>58.15623474121094</v>
+        <v>58.15625381469727</v>
       </c>
       <c r="C92" t="n">
         <v>73.80999755859375</v>
@@ -2611,11 +2623,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>56.92708969116211</v>
+        <v>56.92708206176758</v>
       </c>
       <c r="C93" t="n">
         <v>72.25</v>
@@ -2640,11 +2652,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>58.02231216430664</v>
+        <v>58.02230453491211</v>
       </c>
       <c r="C94" t="n">
         <v>73.63999938964844</v>
@@ -2669,11 +2681,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>58.67964553833008</v>
+        <v>58.67963409423828</v>
       </c>
       <c r="C95" t="n">
         <v>73.5</v>
@@ -2698,11 +2710,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>61.84912872314453</v>
+        <v>61.84913635253906</v>
       </c>
       <c r="C96" t="n">
         <v>77.47000122070312</v>
@@ -2727,11 +2739,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>65.641357421875</v>
+        <v>65.64136505126953</v>
       </c>
       <c r="C97" t="n">
         <v>82.22000122070312</v>
@@ -2756,7 +2768,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
@@ -2785,11 +2797,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>66.54351043701172</v>
+        <v>66.54350280761719</v>
       </c>
       <c r="C99" t="n">
         <v>83.34999847412109</v>
@@ -2814,11 +2826,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>63.64546585083008</v>
+        <v>63.64545822143555</v>
       </c>
       <c r="C100" t="n">
         <v>79.72000122070312</v>
@@ -2843,11 +2855,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>64.8145751953125</v>
+        <v>64.81455993652344</v>
       </c>
       <c r="C101" t="n">
         <v>80.22000122070312</v>
@@ -2872,11 +2884,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>65.80836486816406</v>
+        <v>65.80834197998047</v>
       </c>
       <c r="C102" t="n">
         <v>81.44999694824219</v>
@@ -2901,11 +2913,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>65.31550598144531</v>
+        <v>65.31549072265625</v>
       </c>
       <c r="C103" t="n">
         <v>80.83999633789062</v>
@@ -2930,11 +2942,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>64.05509185791016</v>
+        <v>64.05508422851562</v>
       </c>
       <c r="C104" t="n">
         <v>79.27999877929688</v>
@@ -2959,11 +2971,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>65.49324798583984</v>
+        <v>65.49327087402344</v>
       </c>
       <c r="C105" t="n">
         <v>81.05999755859375</v>
@@ -2988,11 +3000,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>65.70332336425781</v>
+        <v>65.70331573486328</v>
       </c>
       <c r="C106" t="n">
         <v>81.31999969482422</v>
@@ -3017,11 +3029,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>66.43131256103516</v>
+        <v>66.43132781982422</v>
       </c>
       <c r="C107" t="n">
         <v>81.12000274658203</v>
@@ -3046,11 +3058,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>70.69792175292969</v>
+        <v>70.69790649414062</v>
       </c>
       <c r="C108" t="n">
         <v>86.33000183105469</v>
@@ -3075,11 +3087,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>73.13833618164062</v>
+        <v>73.13831329345703</v>
       </c>
       <c r="C109" t="n">
         <v>89.30999755859375</v>
@@ -3104,11 +3116,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>68.81438446044922</v>
+        <v>68.81437683105469</v>
       </c>
       <c r="C110" t="n">
         <v>84.02999877929688</v>
@@ -3133,11 +3145,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>73.72796630859375</v>
+        <v>73.72792816162109</v>
       </c>
       <c r="C111" t="n">
         <v>90.02999877929688</v>
@@ -3162,7 +3174,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
@@ -3191,11 +3203,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>76.68503570556641</v>
+        <v>76.68502044677734</v>
       </c>
       <c r="C113" t="n">
         <v>92.65000152587891</v>
@@ -3220,11 +3232,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>79.49089050292969</v>
+        <v>79.49083709716797</v>
       </c>
       <c r="C114" t="n">
         <v>96.04000091552734</v>
@@ -3249,11 +3261,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>80.10334777832031</v>
+        <v>80.10335540771484</v>
       </c>
       <c r="C115" t="n">
         <v>96.77999877929688</v>
@@ -3278,7 +3290,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
@@ -3307,11 +3319,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>78.02588653564453</v>
+        <v>78.02587890625</v>
       </c>
       <c r="C117" t="n">
         <v>94.26999664306641</v>
@@ -3336,11 +3348,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>81.32832336425781</v>
+        <v>81.32833099365234</v>
       </c>
       <c r="C118" t="n">
         <v>98.26000213623047</v>
@@ -3365,11 +3377,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>89.68114471435547</v>
+        <v>89.68115234375</v>
       </c>
       <c r="C119" t="n">
         <v>107.1999969482422</v>
@@ -3394,11 +3406,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>89.69788360595703</v>
+        <v>89.69789123535156</v>
       </c>
       <c r="C120" t="n">
         <v>107.2200012207031</v>
@@ -3423,11 +3435,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>87.42240142822266</v>
+        <v>87.42239379882812</v>
       </c>
       <c r="C121" t="n">
         <v>104.5</v>
@@ -3452,7 +3464,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
@@ -3481,11 +3493,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>83.87531280517578</v>
+        <v>83.87532806396484</v>
       </c>
       <c r="C123" t="n">
         <v>100.2600021362305</v>
@@ -3510,7 +3522,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
@@ -3539,11 +3551,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>95.38362121582031</v>
+        <v>95.38361358642578</v>
       </c>
       <c r="C125" t="n">
         <v>112.9199981689453</v>
@@ -3568,11 +3580,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>100.4940490722656</v>
+        <v>100.4940567016602</v>
       </c>
       <c r="C126" t="n">
         <v>118.9700012207031</v>
@@ -3597,11 +3609,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>95.69613647460938</v>
+        <v>95.69615936279297</v>
       </c>
       <c r="C127" t="n">
         <v>113.2900009155273</v>
@@ -3626,11 +3638,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>95.29069519042969</v>
+        <v>95.29070281982422</v>
       </c>
       <c r="C128" t="n">
         <v>112.8099975585938</v>
@@ -3655,11 +3667,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>97.14059448242188</v>
+        <v>97.14057922363281</v>
       </c>
       <c r="C129" t="n">
         <v>115</v>
@@ -3684,11 +3696,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>103.1970977783203</v>
+        <v>103.1970901489258</v>
       </c>
       <c r="C130" t="n">
         <v>122.1699981689453</v>
@@ -3713,11 +3725,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>99.20940399169922</v>
+        <v>99.20939636230469</v>
       </c>
       <c r="C131" t="n">
         <v>116.2399978637695</v>
@@ -3742,7 +3754,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
@@ -3771,11 +3783,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>99.968994140625</v>
+        <v>99.96900177001953</v>
       </c>
       <c r="C133" t="n">
         <v>117.129997253418</v>
@@ -3800,11 +3812,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>97.18663787841797</v>
+        <v>97.18663024902344</v>
       </c>
       <c r="C134" t="n">
         <v>113.870002746582</v>
@@ -3829,11 +3841,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>104.5522232055664</v>
+        <v>104.5522384643555</v>
       </c>
       <c r="C135" t="n">
         <v>122.5</v>
@@ -3858,11 +3870,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>102.3160934448242</v>
+        <v>102.3161010742188</v>
       </c>
       <c r="C136" t="n">
         <v>119.879997253418</v>
@@ -3887,11 +3899,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>104.6021194458008</v>
+        <v>104.6021270751953</v>
       </c>
       <c r="C137" t="n">
         <v>121.3000030517578</v>
@@ -3916,11 +3928,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>107.3357315063477</v>
+        <v>107.3357696533203</v>
       </c>
       <c r="C138" t="n">
         <v>124.4700012207031</v>
@@ -3945,11 +3957,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>106.6545028686523</v>
+        <v>106.6545181274414</v>
       </c>
       <c r="C139" t="n">
         <v>123.6800003051758</v>
@@ -3974,11 +3986,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>111.0869293212891</v>
+        <v>111.0869522094727</v>
       </c>
       <c r="C140" t="n">
         <v>128.8200073242188</v>
@@ -4003,7 +4015,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
@@ -4032,11 +4044,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>116.4765930175781</v>
+        <v>116.4765777587891</v>
       </c>
       <c r="C142" t="n">
         <v>135.0700073242188</v>
@@ -4061,11 +4073,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>123.9520645141602</v>
+        <v>123.9520721435547</v>
       </c>
       <c r="C143" t="n">
         <v>142.3600006103516</v>
@@ -4090,11 +4102,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>128.8715209960938</v>
+        <v>128.8715057373047</v>
       </c>
       <c r="C144" t="n">
         <v>148.0099945068359</v>
@@ -4119,7 +4131,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
@@ -4148,11 +4160,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>139.9205322265625</v>
+        <v>139.9205780029297</v>
       </c>
       <c r="C146" t="n">
         <v>160.6999969482422</v>
@@ -4177,7 +4189,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
@@ -4206,11 +4218,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>133.6515960693359</v>
+        <v>133.6515502929688</v>
       </c>
       <c r="C148" t="n">
         <v>153.5</v>
@@ -4235,7 +4247,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
@@ -4264,11 +4276,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>136.7985076904297</v>
+        <v>136.7985229492188</v>
       </c>
       <c r="C150" t="n">
         <v>155.7400054931641</v>
@@ -4293,11 +4305,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>143.6938171386719</v>
+        <v>143.6938323974609</v>
       </c>
       <c r="C151" t="n">
         <v>163.5899963378906</v>
@@ -4322,7 +4334,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
@@ -4351,11 +4363,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>148.50732421875</v>
+        <v>148.5072937011719</v>
       </c>
       <c r="C153" t="n">
         <v>169.0700073242188</v>
@@ -4380,7 +4392,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
@@ -4409,7 +4421,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
@@ -4438,11 +4450,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>145.8314971923828</v>
+        <v>145.8315124511719</v>
       </c>
       <c r="C156" t="n">
         <v>164.5200042724609</v>
@@ -4467,11 +4479,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>124.9921112060547</v>
+        <v>124.9920883178711</v>
       </c>
       <c r="C157" t="n">
         <v>141.0099945068359</v>
@@ -4496,11 +4508,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>136.1076202392578</v>
+        <v>136.1076354980469</v>
       </c>
       <c r="C158" t="n">
         <v>153.5500030517578</v>
@@ -4525,11 +4537,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>143.0482025146484</v>
+        <v>143.0481719970703</v>
       </c>
       <c r="C159" t="n">
         <v>161.3800048828125</v>
@@ -4554,11 +4566,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>156.0251617431641</v>
+        <v>156.0251770019531</v>
       </c>
       <c r="C160" t="n">
         <v>176.0200042724609</v>
@@ -4583,7 +4595,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
@@ -4612,7 +4624,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
@@ -4641,11 +4653,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>165.1377563476562</v>
+        <v>165.1377868652344</v>
       </c>
       <c r="C163" t="n">
         <v>184.7700042724609</v>
@@ -4670,11 +4682,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>172.117919921875</v>
+        <v>172.1179351806641</v>
       </c>
       <c r="C164" t="n">
         <v>192.5800018310547</v>
@@ -4699,11 +4711,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>177.1139831542969</v>
+        <v>177.1139526367188</v>
       </c>
       <c r="C165" t="n">
         <v>198.1699981689453</v>
@@ -4728,7 +4740,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
@@ -4757,11 +4769,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>166.4306945800781</v>
+        <v>166.4307403564453</v>
       </c>
       <c r="C167" t="n">
         <v>185.4199981689453</v>
@@ -4786,11 +4798,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>180.5587310791016</v>
+        <v>180.5587463378906</v>
       </c>
       <c r="C168" t="n">
         <v>201.1600036621094</v>
@@ -4815,11 +4827,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>189.0050506591797</v>
+        <v>189.0050659179688</v>
       </c>
       <c r="C169" t="n">
         <v>210.5700073242188</v>
@@ -4844,11 +4856,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>184.9060821533203</v>
+        <v>184.9060974121094</v>
       </c>
       <c r="C170" t="n">
         <v>205.2100067138672</v>
@@ -4873,11 +4885,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>162.7220153808594</v>
+        <v>162.7220306396484</v>
       </c>
       <c r="C171" t="n">
         <v>180.5899963378906</v>
@@ -4902,11 +4914,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>147.106689453125</v>
+        <v>147.1067047119141</v>
       </c>
       <c r="C172" t="n">
         <v>163.2599945068359</v>
@@ -4931,11 +4943,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>167.6198120117188</v>
+        <v>167.6198272705078</v>
       </c>
       <c r="C173" t="n">
         <v>185.1900024414062</v>
@@ -4960,11 +4972,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>182.4909820556641</v>
+        <v>182.4910125732422</v>
       </c>
       <c r="C174" t="n">
         <v>201.6199951171875</v>
@@ -4989,11 +5001,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>194.3480987548828</v>
+        <v>194.3481140136719</v>
       </c>
       <c r="C175" t="n">
         <v>214.7200012207031</v>
@@ -5018,11 +5030,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>204.1990356445312</v>
+        <v>204.1990966796875</v>
       </c>
       <c r="C176" t="n">
         <v>224.7799987792969</v>
@@ -5047,11 +5059,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>217.9618530273438</v>
+        <v>217.9619293212891</v>
       </c>
       <c r="C177" t="n">
         <v>239.9299926757812</v>
@@ -5076,7 +5088,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
@@ -5105,11 +5117,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>197.8212432861328</v>
+        <v>197.8212127685547</v>
       </c>
       <c r="C179" t="n">
         <v>216.9100036621094</v>
@@ -5134,11 +5146,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>227.1693115234375</v>
+        <v>227.1692962646484</v>
       </c>
       <c r="C180" t="n">
         <v>249.0899963378906</v>
@@ -5163,11 +5175,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>238.2227172851562</v>
+        <v>238.2226715087891</v>
       </c>
       <c r="C181" t="n">
         <v>261.2099914550781</v>
@@ -5192,11 +5204,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>221.3842163085938</v>
+        <v>221.3842468261719</v>
       </c>
       <c r="C182" t="n">
         <v>241.9199981689453</v>
@@ -5221,11 +5233,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>229.6019439697266</v>
+        <v>229.6019592285156</v>
       </c>
       <c r="C183" t="n">
         <v>250.8999938964844</v>
@@ -5250,11 +5262,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>252.8001251220703</v>
+        <v>252.7999725341797</v>
       </c>
       <c r="C184" t="n">
         <v>276.25</v>
@@ -5279,11 +5291,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>266.1766357421875</v>
+        <v>266.1766662597656</v>
       </c>
       <c r="C185" t="n">
         <v>289.9700012207031</v>
@@ -5308,11 +5320,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>259.0074462890625</v>
+        <v>259.0074768066406</v>
       </c>
       <c r="C186" t="n">
         <v>282.1600036621094</v>
@@ -5337,11 +5349,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>270.60107421875</v>
+        <v>270.6011352539062</v>
       </c>
       <c r="C187" t="n">
         <v>294.7900085449219</v>
@@ -5366,11 +5378,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>292.43603515625</v>
+        <v>292.4360961914062</v>
       </c>
       <c r="C188" t="n">
         <v>317.6799926757812</v>
@@ -5395,11 +5407,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>309.8157653808594</v>
+        <v>309.8158569335938</v>
       </c>
       <c r="C189" t="n">
         <v>336.5599975585938</v>
@@ -5424,7 +5436,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
@@ -5453,7 +5465,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
@@ -5482,11 +5494,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>329.9765930175781</v>
+        <v>329.9765319824219</v>
       </c>
       <c r="C192" t="n">
         <v>357.3999938964844</v>
@@ -5511,11 +5523,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>382.7413635253906</v>
+        <v>382.7414245605469</v>
       </c>
       <c r="C193" t="n">
         <v>414.5499877929688</v>
@@ -5540,7 +5552,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
@@ -5569,11 +5581,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>292.528076171875</v>
+        <v>292.5281372070312</v>
       </c>
       <c r="C195" t="n">
         <v>316.0199890136719</v>
@@ -5598,11 +5610,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>312.1614074707031</v>
+        <v>312.1614685058594</v>
       </c>
       <c r="C196" t="n">
         <v>337.2300109863281</v>
@@ -5627,7 +5639,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
@@ -5656,11 +5668,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>277.0961608886719</v>
+        <v>277.0960693359375</v>
       </c>
       <c r="C198" t="n">
         <v>298.4599914550781</v>
@@ -5685,11 +5697,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>257.7757568359375</v>
+        <v>257.7756958007812</v>
       </c>
       <c r="C199" t="n">
         <v>277.6499938964844</v>
@@ -5714,11 +5726,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>285.3492126464844</v>
+        <v>285.3491821289062</v>
       </c>
       <c r="C200" t="n">
         <v>306.260009765625</v>
@@ -5743,11 +5755,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>268.7644958496094</v>
+        <v>268.7645568847656</v>
       </c>
       <c r="C201" t="n">
         <v>288.4599914550781</v>
@@ -5772,7 +5784,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
@@ -5801,11 +5813,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>265.6921691894531</v>
+        <v>265.692138671875</v>
       </c>
       <c r="C203" t="n">
         <v>283.8999938964844</v>
@@ -5830,11 +5842,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>281.6299133300781</v>
+        <v>281.6299438476562</v>
       </c>
       <c r="C204" t="n">
         <v>300.9299926757812</v>
@@ -5859,11 +5871,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>249.7263031005859</v>
+        <v>249.7262878417969</v>
       </c>
       <c r="C205" t="n">
         <v>266.8399963378906</v>
@@ -5888,11 +5900,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>262.2214050292969</v>
+        <v>262.2213745117188</v>
       </c>
       <c r="C206" t="n">
         <v>279.0499877929688</v>
@@ -5917,7 +5929,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
@@ -5946,11 +5958,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>268.57373046875</v>
+        <v>268.5737915039062</v>
       </c>
       <c r="C208" t="n">
         <v>285.8099975585938</v>
@@ -5975,7 +5987,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
@@ -6004,11 +6016,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>288.599853515625</v>
+        <v>288.5998840332031</v>
       </c>
       <c r="C210" t="n">
         <v>305.9200134277344</v>
@@ -6033,11 +6045,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>291.1092529296875</v>
+        <v>291.1092224121094</v>
       </c>
       <c r="C211" t="n">
         <v>308.5799865722656</v>
@@ -6062,7 +6074,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
@@ -6091,7 +6103,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
@@ -6120,7 +6132,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
@@ -6149,11 +6161,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>282.4535827636719</v>
+        <v>282.4536437988281</v>
       </c>
       <c r="C215" t="n">
         <v>297.0899963378906</v>
@@ -6178,11 +6190,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>316.7275390625</v>
+        <v>316.7275695800781</v>
       </c>
       <c r="C216" t="n">
         <v>333.1400146484375</v>
@@ -6207,11 +6219,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>333.6221313476562</v>
+        <v>333.6221008300781</v>
       </c>
       <c r="C217" t="n">
         <v>350.9100036621094</v>
@@ -6236,7 +6248,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6265,7 +6277,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
@@ -6294,11 +6306,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>330.7372436523438</v>
+        <v>330.7372741699219</v>
       </c>
       <c r="C220" t="n">
         <v>346.6099853515625</v>
@@ -6323,7 +6335,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6352,7 +6364,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -6381,11 +6393,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>290.6365966796875</v>
+        <v>290.6365661621094</v>
       </c>
       <c r="C223" t="n">
         <v>303.4100036621094</v>
@@ -6410,11 +6422,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>318.0899658203125</v>
+        <v>318.0899963378906</v>
       </c>
       <c r="C224" t="n">
         <v>330.6199951171875</v>
@@ -6439,11 +6451,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>328.9906005859375</v>
+        <v>328.9906311035156</v>
       </c>
       <c r="C225" t="n">
         <v>341.9500122070312</v>
@@ -6468,7 +6480,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6497,11 +6509,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>333.1021728515625</v>
+        <v>333.1022033691406</v>
       </c>
       <c r="C227" t="n">
         <v>344.8200073242188</v>
@@ -6526,7 +6538,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6555,11 +6567,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>339.8352966308594</v>
+        <v>339.8353271484375</v>
       </c>
       <c r="C229" t="n">
         <v>351.7900085449219</v>
@@ -6584,7 +6596,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6613,7 +6625,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6642,7 +6654,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6671,7 +6683,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6700,11 +6712,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>308.8784790039062</v>
+        <v>308.8784484863281</v>
       </c>
       <c r="C234" t="n">
         <v>316.8200073242188</v>
@@ -6729,7 +6741,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6758,7 +6770,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6787,11 +6799,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>254.7210693359375</v>
+        <v>254.7210845947266</v>
       </c>
       <c r="C237" t="n">
         <v>259.9700012207031</v>
@@ -6816,7 +6828,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6845,7 +6857,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6874,11 +6886,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>244.9523773193359</v>
+        <v>244.952392578125</v>
       </c>
       <c r="C240" t="n">
         <v>250</v>
@@ -6903,11 +6915,11 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>262.8828735351562</v>
+        <v>262.8829040527344</v>
       </c>
       <c r="C241" t="n">
         <v>268.2999877929688</v>
@@ -6932,7 +6944,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6961,11 +6973,11 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>204.5058441162109</v>
+        <v>204.505859375</v>
       </c>
       <c r="C243" t="n">
         <v>208.7200012207031</v>
@@ -6990,11 +7002,11 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
-        <v>194.2864227294922</v>
+        <v>194.2864379882812</v>
       </c>
       <c r="C244" t="n">
         <v>198.2899932861328</v>
@@ -7019,7 +7031,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7048,7 +7060,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7077,7 +7089,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7106,7 +7118,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7135,7 +7147,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7164,32 +7176,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>183.5200042724609</v>
+        <v>177.4100036621094</v>
       </c>
       <c r="C250" t="n">
-        <v>183.5200042724609</v>
+        <v>177.4100036621094</v>
       </c>
       <c r="D250" t="n">
-        <v>78044600</v>
+        <v>82679200</v>
       </c>
       <c r="E250" t="n">
         <v>12.52</v>
       </c>
       <c r="F250" t="n">
-        <v>14.6581473061071</v>
+        <v>14.17012808802791</v>
       </c>
       <c r="G250" t="n">
         <v>612213453</v>
       </c>
       <c r="H250" t="n">
-        <v>112353415510.2181</v>
+        <v>108612790938.7226</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1274793940210915</v>
+        <v>0.1350496294958092</v>
       </c>
     </row>
   </sheetData>
@@ -7221,75 +7233,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39692</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39782</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40165</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7325,13 +7337,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39783</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39872</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40263</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7367,13 +7379,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39873</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39964</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40354</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7409,13 +7421,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39965</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40056</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40477</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7442,7 +7454,7 @@
       <c r="I5" t="n">
         <v>2.44</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>40477</v>
       </c>
       <c r="K5" t="n">
@@ -7455,13 +7467,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40057</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40147</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40165</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7488,7 +7500,7 @@
       <c r="I6" t="n">
         <v>2.37</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>40477</v>
       </c>
       <c r="K6" t="n">
@@ -7501,13 +7513,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40148</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40237</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40263</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7534,7 +7546,7 @@
       <c r="I7" t="n">
         <v>2.34</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40477</v>
       </c>
       <c r="K7" t="n">
@@ -7547,13 +7559,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40238</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40329</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40354</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7580,7 +7592,7 @@
       <c r="I8" t="n">
         <v>2.39</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40477</v>
       </c>
       <c r="K8" t="n">
@@ -7593,13 +7605,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40330</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40421</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40477</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7626,7 +7638,7 @@
       <c r="I9" t="n">
         <v>2.66</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40477</v>
       </c>
       <c r="K9" t="n">
@@ -7639,13 +7651,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40422</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40512</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40532</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7672,7 +7684,7 @@
       <c r="I10" t="n">
         <v>2.8</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40532</v>
       </c>
       <c r="K10" t="n">
@@ -7685,13 +7697,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40513</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40602</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40627</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7718,7 +7730,7 @@
       <c r="I11" t="n">
         <v>2.95</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40627</v>
       </c>
       <c r="K11" t="n">
@@ -7731,13 +7743,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40603</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40694</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40718</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7764,7 +7776,7 @@
       <c r="I12" t="n">
         <v>3.15</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40718</v>
       </c>
       <c r="K12" t="n">
@@ -7777,13 +7789,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40695</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40786</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40837</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7810,7 +7822,7 @@
       <c r="I13" t="n">
         <v>3.4</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40837</v>
       </c>
       <c r="K13" t="n">
@@ -7823,13 +7835,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40787</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40877</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40897</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7856,7 +7868,7 @@
       <c r="I14" t="n">
         <v>3.55</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40897</v>
       </c>
       <c r="K14" t="n">
@@ -7869,13 +7881,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40878</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40968</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40991</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7902,7 +7914,7 @@
       <c r="I15" t="n">
         <v>3.77</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40991</v>
       </c>
       <c r="K15" t="n">
@@ -7915,13 +7927,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40969</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41060</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41089</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7948,7 +7960,7 @@
       <c r="I16" t="n">
         <v>3.87</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41089</v>
       </c>
       <c r="K16" t="n">
@@ -7961,13 +7973,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41061</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41152</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41212</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7994,7 +8006,7 @@
       <c r="I17" t="n">
         <v>3.84</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41212</v>
       </c>
       <c r="K17" t="n">
@@ -8007,13 +8019,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41153</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41243</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41263</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8040,7 +8052,7 @@
       <c r="I18" t="n">
         <v>3.94</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41263</v>
       </c>
       <c r="K18" t="n">
@@ -8053,13 +8065,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41244</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41333</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41361</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8086,7 +8098,7 @@
       <c r="I19" t="n">
         <v>4.619999999999999</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41361</v>
       </c>
       <c r="K19" t="n">
@@ -8099,13 +8111,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41334</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41425</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41453</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8132,7 +8144,7 @@
       <c r="I20" t="n">
         <v>4.8</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41453</v>
       </c>
       <c r="K20" t="n">
@@ -8145,13 +8157,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41426</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41517</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41576</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8178,7 +8190,7 @@
       <c r="I21" t="n">
         <v>4.93</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41576</v>
       </c>
       <c r="K21" t="n">
@@ -8191,13 +8203,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41518</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41608</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41627</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8224,7 +8236,7 @@
       <c r="I22" t="n">
         <v>5.02</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41627</v>
       </c>
       <c r="K22" t="n">
@@ -8237,13 +8249,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41609</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41698</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41725</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8270,7 +8282,7 @@
       <c r="I23" t="n">
         <v>4.4</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41725</v>
       </c>
       <c r="K23" t="n">
@@ -8283,13 +8295,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41699</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41790</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41816</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8316,7 +8328,7 @@
       <c r="I24" t="n">
         <v>4.45</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41816</v>
       </c>
       <c r="K24" t="n">
@@ -8329,13 +8341,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41791</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41882</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41936</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8362,7 +8374,7 @@
       <c r="I25" t="n">
         <v>4.52</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41936</v>
       </c>
       <c r="K25" t="n">
@@ -8375,13 +8387,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41883</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41973</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41991</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8408,7 +8420,7 @@
       <c r="I26" t="n">
         <v>4.66</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41991</v>
       </c>
       <c r="K26" t="n">
@@ -8421,13 +8433,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41974</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42063</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42089</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8454,7 +8466,7 @@
       <c r="I27" t="n">
         <v>4.71</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42089</v>
       </c>
       <c r="K27" t="n">
@@ -8467,13 +8479,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42064</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42155</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42180</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8500,7 +8512,7 @@
       <c r="I28" t="n">
         <v>4.69</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42180</v>
       </c>
       <c r="K28" t="n">
@@ -8513,13 +8525,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42156</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42247</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8546,7 +8558,7 @@
       <c r="I29" t="n">
         <v>4.76</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="K29" t="n">
@@ -8559,13 +8571,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42248</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42338</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42355</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8592,7 +8604,7 @@
       <c r="I30" t="n">
         <v>4.75</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42355</v>
       </c>
       <c r="K30" t="n">
@@ -8605,13 +8617,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42339</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42429</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42453</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8638,7 +8650,7 @@
       <c r="I31" t="n">
         <v>5.75</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42453</v>
       </c>
       <c r="K31" t="n">
@@ -8651,13 +8663,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42430</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42521</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42544</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8684,7 +8696,7 @@
       <c r="I32" t="n">
         <v>5.92</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42544</v>
       </c>
       <c r="K32" t="n">
@@ -8697,13 +8709,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42522</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42613</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42671</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8730,7 +8742,7 @@
       <c r="I33" t="n">
         <v>6.449999999999999</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42671</v>
       </c>
       <c r="K33" t="n">
@@ -8743,13 +8755,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42614</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42704</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42725</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8776,7 +8788,7 @@
       <c r="I34" t="n">
         <v>6.75</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42725</v>
       </c>
       <c r="K34" t="n">
@@ -8789,13 +8801,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42705</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42794</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42817</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8822,7 +8834,7 @@
       <c r="I35" t="n">
         <v>6</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42817</v>
       </c>
       <c r="K35" t="n">
@@ -8835,13 +8847,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42795</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42886</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42908</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8868,7 +8880,7 @@
       <c r="I36" t="n">
         <v>5.64</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42908</v>
       </c>
       <c r="K36" t="n">
@@ -8881,13 +8893,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42887</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42978</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8914,7 +8926,7 @@
       <c r="I37" t="n">
         <v>5.44</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="K37" t="n">
@@ -8927,13 +8939,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42979</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43069</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43090</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8960,7 +8972,7 @@
       <c r="I38" t="n">
         <v>5.65</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43090</v>
       </c>
       <c r="K38" t="n">
@@ -8973,13 +8985,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43070</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43159</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43181</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -9006,7 +9018,7 @@
       <c r="I39" t="n">
         <v>5.69</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43181</v>
       </c>
       <c r="K39" t="n">
@@ -9019,13 +9031,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43160</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43251</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43279</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9052,7 +9064,7 @@
       <c r="I40" t="n">
         <v>6.24</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43279</v>
       </c>
       <c r="K40" t="n">
@@ -9065,13 +9077,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43252</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43343</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43397</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9098,7 +9110,7 @@
       <c r="I41" t="n">
         <v>6.34</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43397</v>
       </c>
       <c r="K41" t="n">
@@ -9111,13 +9123,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43344</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43434</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43454</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9144,7 +9156,7 @@
       <c r="I42" t="n">
         <v>6.51</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43454</v>
       </c>
       <c r="K42" t="n">
@@ -9157,13 +9169,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43435</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43524</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43552</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9190,7 +9202,7 @@
       <c r="I43" t="n">
         <v>6.87</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43552</v>
       </c>
       <c r="K43" t="n">
@@ -9203,13 +9215,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43525</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43616</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43643</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9236,7 +9248,7 @@
       <c r="I44" t="n">
         <v>7.2</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43643</v>
       </c>
       <c r="K44" t="n">
@@ -9249,13 +9261,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43617</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43708</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43767</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9282,7 +9294,7 @@
       <c r="I45" t="n">
         <v>7.36</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43767</v>
       </c>
       <c r="K45" t="n">
@@ -9295,13 +9307,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43709</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43799</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43818</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9328,7 +9340,7 @@
       <c r="I46" t="n">
         <v>7.49</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43818</v>
       </c>
       <c r="K46" t="n">
@@ -9341,13 +9353,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43800</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43890</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43909</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9374,7 +9386,7 @@
       <c r="I47" t="n">
         <v>7.67</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43909</v>
       </c>
       <c r="K47" t="n">
@@ -9387,13 +9399,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43891</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43982</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44007</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9420,7 +9432,7 @@
       <c r="I48" t="n">
         <v>7.64</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44007</v>
       </c>
       <c r="K48" t="n">
@@ -9433,13 +9445,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43983</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44074</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44126</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9466,7 +9478,7 @@
       <c r="I49" t="n">
         <v>7.89</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44126</v>
       </c>
       <c r="K49" t="n">
@@ -9479,13 +9491,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44075</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44165</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44182</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9512,7 +9524,7 @@
       <c r="I50" t="n">
         <v>8.119999999999999</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44182</v>
       </c>
       <c r="K50" t="n">
@@ -9525,13 +9537,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44166</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44255</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44273</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9558,7 +9570,7 @@
       <c r="I51" t="n">
         <v>8.44</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44273</v>
       </c>
       <c r="K51" t="n">
@@ -9571,13 +9583,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44256</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44347</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44371</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9604,7 +9616,7 @@
       <c r="I52" t="n">
         <v>8.94</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44371</v>
       </c>
       <c r="K52" t="n">
@@ -9617,13 +9629,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44348</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44439</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44484</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9650,7 +9662,7 @@
       <c r="I53" t="n">
         <v>9.15</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44484</v>
       </c>
       <c r="K53" t="n">
@@ -9663,13 +9675,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44440</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44530</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44546</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9696,7 +9708,7 @@
       <c r="I54" t="n">
         <v>9.609999999999999</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44546</v>
       </c>
       <c r="K54" t="n">
@@ -9709,13 +9721,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44531</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44620</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44637</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9742,7 +9754,7 @@
       <c r="I55" t="n">
         <v>9.92</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44637</v>
       </c>
       <c r="K55" t="n">
@@ -9755,13 +9767,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44621</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44712</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44735</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9788,7 +9800,7 @@
       <c r="I56" t="n">
         <v>10.31</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44735</v>
       </c>
       <c r="K56" t="n">
@@ -9801,13 +9813,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44713</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44804</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44846</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9834,7 +9846,7 @@
       <c r="I57" t="n">
         <v>10.71</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44846</v>
       </c>
       <c r="K57" t="n">
@@ -9847,13 +9859,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44805</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44895</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44911</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9880,7 +9892,7 @@
       <c r="I58" t="n">
         <v>11.01</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44911</v>
       </c>
       <c r="K58" t="n">
@@ -9893,13 +9905,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44896</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44985</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45008</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9926,7 +9938,7 @@
       <c r="I59" t="n">
         <v>10.86</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45008</v>
       </c>
       <c r="K59" t="n">
@@ -9939,13 +9951,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44986</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45077</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45099</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9972,7 +9984,7 @@
       <c r="I60" t="n">
         <v>11.22</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45099</v>
       </c>
       <c r="K60" t="n">
@@ -9985,13 +9997,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45078</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45169</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45211</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10018,7 +10030,7 @@
       <c r="I61" t="n">
         <v>10.77</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45211</v>
       </c>
       <c r="K61" t="n">
@@ -10031,13 +10043,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45170</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45260</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45279</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10064,7 +10076,7 @@
       <c r="I62" t="n">
         <v>10.79</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45279</v>
       </c>
       <c r="K62" t="n">
@@ -10077,13 +10089,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45261</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45351</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45372</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10110,7 +10122,7 @@
       <c r="I63" t="n">
         <v>11.03</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45372</v>
       </c>
       <c r="K63" t="n">
@@ -10123,13 +10135,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45352</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45443</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45463</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10156,7 +10168,7 @@
       <c r="I64" t="n">
         <v>10.92</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45463</v>
       </c>
       <c r="K64" t="n">
@@ -10169,13 +10181,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45444</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45535</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45575</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10202,7 +10214,7 @@
       <c r="I65" t="n">
         <v>11.43</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45575</v>
       </c>
       <c r="K65" t="n">
@@ -10215,13 +10227,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45536</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45626</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45645</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10248,7 +10260,7 @@
       <c r="I66" t="n">
         <v>11.92</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45645</v>
       </c>
       <c r="K66" t="n">
@@ -10261,13 +10273,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45627</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45716</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45736</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10294,7 +10306,7 @@
       <c r="I67" t="n">
         <v>12.11</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45736</v>
       </c>
       <c r="K67" t="n">
@@ -10307,13 +10319,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45717</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45808</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45828</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10340,7 +10352,7 @@
       <c r="I68" t="n">
         <v>12.56</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45828</v>
       </c>
       <c r="K68" t="n">
@@ -10353,13 +10365,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45809</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45900</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45940</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10386,7 +10398,7 @@
       <c r="I69" t="n">
         <v>12.15</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45940</v>
       </c>
       <c r="K69" t="n">
@@ -10399,13 +10411,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45901</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45991</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>46009</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10432,7 +10444,7 @@
       <c r="I70" t="n">
         <v>12.1</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46009</v>
       </c>
       <c r="K70" t="n">
@@ -10445,13 +10457,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45992</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46100</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10478,7 +10490,7 @@
       <c r="I71" t="n">
         <v>12.21</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46100</v>
       </c>
       <c r="K71" t="n">
@@ -10491,13 +10503,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46173</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46191</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10524,7 +10536,7 @@
       <c r="I72" t="n">
         <v>12.52</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46191</v>
       </c>
       <c r="K72" t="n">
@@ -10562,57 +10574,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39782</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40165</v>
       </c>
       <c r="C2" t="n">
@@ -10646,10 +10658,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40147</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40165</v>
       </c>
       <c r="C3" t="n">
@@ -10683,10 +10695,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39872</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40263</v>
       </c>
       <c r="C4" t="n">
@@ -10720,10 +10732,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40237</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40263</v>
       </c>
       <c r="C5" t="n">
@@ -10757,10 +10769,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39964</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40354</v>
       </c>
       <c r="C6" t="n">
@@ -10794,10 +10806,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40329</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40354</v>
       </c>
       <c r="C7" t="n">
@@ -10831,10 +10843,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40056</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40477</v>
       </c>
       <c r="C8" t="n">
@@ -10868,10 +10880,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>39691</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40477</v>
       </c>
       <c r="C9" t="n">
@@ -10905,10 +10917,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40421</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40477</v>
       </c>
       <c r="C10" t="n">
@@ -10942,10 +10954,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40512</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40532</v>
       </c>
       <c r="C11" t="n">
@@ -10979,10 +10991,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40602</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40627</v>
       </c>
       <c r="C12" t="n">
@@ -11016,10 +11028,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40694</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40718</v>
       </c>
       <c r="C13" t="n">
@@ -11053,10 +11065,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40786</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40837</v>
       </c>
       <c r="C14" t="n">
@@ -11090,10 +11102,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40877</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40897</v>
       </c>
       <c r="C15" t="n">
@@ -11127,10 +11139,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40968</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40991</v>
       </c>
       <c r="C16" t="n">
@@ -11164,10 +11176,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41060</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41089</v>
       </c>
       <c r="C17" t="n">
@@ -11201,10 +11213,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41152</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41212</v>
       </c>
       <c r="C18" t="n">
@@ -11238,10 +11250,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41243</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41263</v>
       </c>
       <c r="C19" t="n">
@@ -11275,10 +11287,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41333</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41361</v>
       </c>
       <c r="C20" t="n">
@@ -11312,10 +11324,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41425</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41453</v>
       </c>
       <c r="C21" t="n">
@@ -11349,10 +11361,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41517</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41576</v>
       </c>
       <c r="C22" t="n">
@@ -11386,10 +11398,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41608</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41627</v>
       </c>
       <c r="C23" t="n">
@@ -11423,10 +11435,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41698</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41725</v>
       </c>
       <c r="C24" t="n">
@@ -11460,10 +11472,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41790</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41816</v>
       </c>
       <c r="C25" t="n">
@@ -11497,10 +11509,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41882</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41936</v>
       </c>
       <c r="C26" t="n">
@@ -11534,10 +11546,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41973</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>41991</v>
       </c>
       <c r="C27" t="n">
@@ -11571,10 +11583,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42063</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42089</v>
       </c>
       <c r="C28" t="n">
@@ -11608,10 +11620,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42155</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42180</v>
       </c>
       <c r="C29" t="n">
@@ -11645,10 +11657,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42247</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="C30" t="n">
@@ -11682,10 +11694,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42338</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42355</v>
       </c>
       <c r="C31" t="n">
@@ -11719,10 +11731,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42429</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42453</v>
       </c>
       <c r="C32" t="n">
@@ -11756,10 +11768,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42521</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42544</v>
       </c>
       <c r="C33" t="n">
@@ -11793,10 +11805,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42613</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42671</v>
       </c>
       <c r="C34" t="n">
@@ -11830,10 +11842,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42704</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42725</v>
       </c>
       <c r="C35" t="n">
@@ -11867,10 +11879,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42794</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42817</v>
       </c>
       <c r="C36" t="n">
@@ -11904,10 +11916,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42886</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42908</v>
       </c>
       <c r="C37" t="n">
@@ -11941,10 +11953,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42978</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="C38" t="n">
@@ -11978,10 +11990,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43069</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43090</v>
       </c>
       <c r="C39" t="n">
@@ -12015,10 +12027,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43159</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43181</v>
       </c>
       <c r="C40" t="n">
@@ -12052,10 +12064,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43251</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43279</v>
       </c>
       <c r="C41" t="n">
@@ -12089,10 +12101,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43343</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43397</v>
       </c>
       <c r="C42" t="n">
@@ -12126,10 +12138,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43434</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43454</v>
       </c>
       <c r="C43" t="n">
@@ -12163,10 +12175,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43524</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43552</v>
       </c>
       <c r="C44" t="n">
@@ -12200,10 +12212,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43616</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43643</v>
       </c>
       <c r="C45" t="n">
@@ -12237,10 +12249,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43708</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43767</v>
       </c>
       <c r="C46" t="n">
@@ -12274,10 +12286,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43799</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43818</v>
       </c>
       <c r="C47" t="n">
@@ -12311,10 +12323,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43890</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43909</v>
       </c>
       <c r="C48" t="n">
@@ -12348,10 +12360,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43982</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44007</v>
       </c>
       <c r="C49" t="n">
@@ -12385,10 +12397,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44074</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44126</v>
       </c>
       <c r="C50" t="n">
@@ -12422,10 +12434,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44165</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44182</v>
       </c>
       <c r="C51" t="n">
@@ -12459,10 +12471,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44255</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44273</v>
       </c>
       <c r="C52" t="n">
@@ -12496,10 +12508,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44347</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44371</v>
       </c>
       <c r="C53" t="n">
@@ -12533,10 +12545,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44439</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44484</v>
       </c>
       <c r="C54" t="n">
@@ -12570,10 +12582,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44530</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44546</v>
       </c>
       <c r="C55" t="n">
@@ -12607,10 +12619,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44620</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44637</v>
       </c>
       <c r="C56" t="n">
@@ -12644,10 +12656,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44712</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44735</v>
       </c>
       <c r="C57" t="n">
@@ -12681,10 +12693,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44804</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44846</v>
       </c>
       <c r="C58" t="n">
@@ -12718,10 +12730,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44895</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44911</v>
       </c>
       <c r="C59" t="n">
@@ -12755,10 +12767,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44985</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45008</v>
       </c>
       <c r="C60" t="n">
@@ -12792,10 +12804,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45077</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45099</v>
       </c>
       <c r="C61" t="n">
@@ -12829,10 +12841,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45169</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45211</v>
       </c>
       <c r="C62" t="n">
@@ -12866,10 +12878,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45260</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45279</v>
       </c>
       <c r="C63" t="n">
@@ -12903,10 +12915,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45351</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45372</v>
       </c>
       <c r="C64" t="n">
@@ -12940,10 +12952,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45443</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45463</v>
       </c>
       <c r="C65" t="n">
@@ -12977,10 +12989,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45535</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45575</v>
       </c>
       <c r="C66" t="n">
@@ -13014,10 +13026,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45626</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45645</v>
       </c>
       <c r="C67" t="n">
@@ -13051,10 +13063,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45716</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45736</v>
       </c>
       <c r="C68" t="n">
@@ -13088,10 +13100,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45808</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45828</v>
       </c>
       <c r="C69" t="n">
@@ -13125,10 +13137,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45900</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45940</v>
       </c>
       <c r="C70" t="n">
@@ -13162,10 +13174,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45991</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46009</v>
       </c>
       <c r="C71" t="n">
@@ -13199,10 +13211,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46081</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46100</v>
       </c>
       <c r="C72" t="n">
@@ -13236,10 +13248,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46173</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46191</v>
       </c>
       <c r="C73" t="n">
@@ -13291,12 +13303,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/ACN.xlsx
+++ b/salidas/empresas/ACN.xlsx
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>22.63822746276855</v>
+        <v>22.63821983337402</v>
       </c>
       <c r="C3" t="n">
         <v>32.65999984741211</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>20.84296798706055</v>
+        <v>20.84297180175781</v>
       </c>
       <c r="C4" t="n">
         <v>30.06999969482422</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>20.14982032775879</v>
+        <v>20.14981460571289</v>
       </c>
       <c r="C5" t="n">
         <v>29.06999969482422</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>19.51212501525879</v>
+        <v>19.51212120056152</v>
       </c>
       <c r="C6" t="n">
         <v>28.14999961853027</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>19.62995910644531</v>
+        <v>19.62996292114258</v>
       </c>
       <c r="C7" t="n">
         <v>28.31999969482422</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>20.28151512145996</v>
+        <v>20.28152084350586</v>
       </c>
       <c r="C8" t="n">
         <v>29.26000022888184</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>20.55877876281738</v>
+        <v>20.55877685546875</v>
       </c>
       <c r="C9" t="n">
         <v>29.65999984741211</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>21.97972869873047</v>
+        <v>21.97973251342773</v>
       </c>
       <c r="C10" t="n">
         <v>31.70999908447266</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>23.06472587585449</v>
+        <v>23.06473159790039</v>
       </c>
       <c r="C11" t="n">
         <v>32.90999984741211</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>23.6184024810791</v>
+        <v>23.61839866638184</v>
       </c>
       <c r="C12" t="n">
         <v>33.70000076293945</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>25.88212203979492</v>
+        <v>25.88211822509766</v>
       </c>
       <c r="C13" t="n">
         <v>36.93000030517578</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>26.45681190490723</v>
+        <v>26.45682144165039</v>
       </c>
       <c r="C14" t="n">
         <v>37.75</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>25.07615089416504</v>
+        <v>25.07614898681641</v>
       </c>
       <c r="C15" t="n">
         <v>35.77999877929688</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>27.40295028686523</v>
+        <v>27.4029369354248</v>
       </c>
       <c r="C17" t="n">
         <v>39.09999847412109</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>28.69248962402344</v>
+        <v>28.6924934387207</v>
       </c>
       <c r="C18" t="n">
         <v>40.93999862670898</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>30.05913925170898</v>
+        <v>30.05914878845215</v>
       </c>
       <c r="C19" t="n">
         <v>42.88999938964844</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>29.5264949798584</v>
+        <v>29.52649879455566</v>
       </c>
       <c r="C20" t="n">
         <v>42.13000106811523</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>28.88171195983887</v>
+        <v>28.88172721862793</v>
       </c>
       <c r="C21" t="n">
         <v>41.20999908447266</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>28.20892715454102</v>
+        <v>28.20891189575195</v>
       </c>
       <c r="C22" t="n">
         <v>40.25</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>27.65627670288086</v>
+        <v>27.65628051757812</v>
       </c>
       <c r="C23" t="n">
         <v>39.04999923706055</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>24.4763355255127</v>
+        <v>24.47633743286133</v>
       </c>
       <c r="C24" t="n">
         <v>34.56000137329102</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>25.51742744445801</v>
+        <v>25.51742362976074</v>
       </c>
       <c r="C25" t="n">
         <v>36.02999877929688</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>24.51882934570312</v>
+        <v>24.51883316040039</v>
       </c>
       <c r="C26" t="n">
         <v>34.61999893188477</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>24.96501922607422</v>
+        <v>24.96501159667969</v>
       </c>
       <c r="C27" t="n">
         <v>35.25</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>24.90836524963379</v>
+        <v>24.90835380554199</v>
       </c>
       <c r="C28" t="n">
         <v>35.16999816894531</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>26.59393501281738</v>
+        <v>26.59392738342285</v>
       </c>
       <c r="C29" t="n">
         <v>37.54999923706055</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>28.90983963012695</v>
+        <v>28.90984535217285</v>
       </c>
       <c r="C30" t="n">
         <v>40.81999969482422</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>29.5755672454834</v>
+        <v>29.57556915283203</v>
       </c>
       <c r="C32" t="n">
         <v>41.7599983215332</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>29.29228591918945</v>
+        <v>29.29228782653809</v>
       </c>
       <c r="C33" t="n">
         <v>41.36000061035156</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>26.91263198852539</v>
+        <v>26.91263961791992</v>
       </c>
       <c r="C34" t="n">
         <v>38</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>23.77938652038574</v>
+        <v>23.77939605712891</v>
       </c>
       <c r="C35" t="n">
         <v>33.04999923706055</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>22.29003524780273</v>
+        <v>22.29003143310547</v>
       </c>
       <c r="C36" t="n">
         <v>30.97999954223633</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>23.59232330322266</v>
+        <v>23.59232902526855</v>
       </c>
       <c r="C37" t="n">
         <v>32.79000091552734</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>22.70734596252441</v>
+        <v>22.70734405517578</v>
       </c>
       <c r="C38" t="n">
         <v>31.55999946594238</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>21.00214004516602</v>
+        <v>21.00213432312012</v>
       </c>
       <c r="C39" t="n">
         <v>29.19000053405762</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>21.1748104095459</v>
+        <v>21.17481422424316</v>
       </c>
       <c r="C41" t="n">
         <v>29.43000030517578</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>21.53456878662109</v>
+        <v>21.53456115722656</v>
       </c>
       <c r="C42" t="n">
         <v>29.93000030517578</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>24.07439613342285</v>
+        <v>24.07439231872559</v>
       </c>
       <c r="C43" t="n">
         <v>33.45999908447266</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>25.23277282714844</v>
+        <v>25.2327823638916</v>
       </c>
       <c r="C44" t="n">
         <v>35.06999969482422</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>23.74342918395996</v>
+        <v>23.74342155456543</v>
       </c>
       <c r="C45" t="n">
         <v>33</v>
@@ -1334,7 +1334,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>26.81567573547363</v>
+        <v>26.81566619873047</v>
       </c>
       <c r="C46" t="n">
         <v>37.27000045776367</v>
@@ -1353,7 +1353,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>27.19640350341797</v>
+        <v>27.19640731811523</v>
       </c>
       <c r="C47" t="n">
         <v>37.08000183105469</v>
@@ -1372,7 +1372,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>30.10088729858398</v>
+        <v>30.10088157653809</v>
       </c>
       <c r="C48" t="n">
         <v>41.04000091552734</v>
@@ -1391,7 +1391,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>30.43827056884766</v>
+        <v>30.43826866149902</v>
       </c>
       <c r="C49" t="n">
         <v>41.5</v>
@@ -1416,7 +1416,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>30.06420516967773</v>
+        <v>30.0642032623291</v>
       </c>
       <c r="C50" t="n">
         <v>40.9900016784668</v>
@@ -1441,7 +1441,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>29.31608963012695</v>
+        <v>29.31609153747559</v>
       </c>
       <c r="C51" t="n">
         <v>39.97000122070312</v>
@@ -1466,7 +1466,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>30.7683219909668</v>
+        <v>30.76833152770996</v>
       </c>
       <c r="C52" t="n">
         <v>41.95000076293945</v>
@@ -1491,7 +1491,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>32.28879165649414</v>
+        <v>32.28878402709961</v>
       </c>
       <c r="C53" t="n">
         <v>43.63999938964844</v>
@@ -1516,7 +1516,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>27.76067161560059</v>
+        <v>27.76066017150879</v>
       </c>
       <c r="C54" t="n">
         <v>37.52000045776367</v>
@@ -1541,7 +1541,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>28.59673500061035</v>
+        <v>28.59674453735352</v>
       </c>
       <c r="C55" t="n">
         <v>38.65000152587891</v>
@@ -1566,7 +1566,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>29.3292179107666</v>
+        <v>29.32923698425293</v>
       </c>
       <c r="C56" t="n">
         <v>39.63999938964844</v>
@@ -1591,7 +1591,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>27.07996559143066</v>
+        <v>27.0799617767334</v>
       </c>
       <c r="C57" t="n">
         <v>36.59999847412109</v>
@@ -1616,7 +1616,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>31.43791770935059</v>
+        <v>31.43790817260742</v>
       </c>
       <c r="C58" t="n">
         <v>42.4900016784668</v>
@@ -1641,7 +1641,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>33.40922927856445</v>
+        <v>33.40921401977539</v>
       </c>
       <c r="C59" t="n">
         <v>44.70999908447266</v>
@@ -1728,7 +1728,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>38.4605827331543</v>
+        <v>38.46060180664062</v>
       </c>
       <c r="C62" t="n">
         <v>51.47000122070312</v>
@@ -1757,7 +1757,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>38.46805572509766</v>
+        <v>38.46805191040039</v>
       </c>
       <c r="C63" t="n">
         <v>51.47999954223633</v>
@@ -1786,7 +1786,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>41.07594680786133</v>
+        <v>41.07595062255859</v>
       </c>
       <c r="C64" t="n">
         <v>54.97000122070312</v>
@@ -1815,7 +1815,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>43.03680801391602</v>
+        <v>43.03680419921875</v>
       </c>
       <c r="C65" t="n">
         <v>57.13000106811523</v>
@@ -1844,7 +1844,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>43.23267364501953</v>
+        <v>43.23266983032227</v>
       </c>
       <c r="C66" t="n">
         <v>57.38999938964844</v>
@@ -1873,7 +1873,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>45.51520538330078</v>
+        <v>45.51521301269531</v>
       </c>
       <c r="C67" t="n">
         <v>60.41999816894531</v>
@@ -1902,7 +1902,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>44.55096054077148</v>
+        <v>44.55096435546875</v>
       </c>
       <c r="C68" t="n">
         <v>59.13999938964844</v>
@@ -1931,7 +1931,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>40.37007522583008</v>
+        <v>40.37009048461914</v>
       </c>
       <c r="C69" t="n">
         <v>53.59000015258789</v>
@@ -1960,7 +1960,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>39.6845588684082</v>
+        <v>39.68456649780273</v>
       </c>
       <c r="C70" t="n">
         <v>52.68000030517578</v>
@@ -1989,7 +1989,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>45.93849945068359</v>
+        <v>45.9384880065918</v>
       </c>
       <c r="C71" t="n">
         <v>60.2599983215332</v>
@@ -2018,7 +2018,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>44.16223526000977</v>
+        <v>44.16225051879883</v>
       </c>
       <c r="C72" t="n">
         <v>57.93000030517578</v>
@@ -2047,7 +2047,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>40.57925415039062</v>
+        <v>40.57924652099609</v>
       </c>
       <c r="C73" t="n">
         <v>53.22999954223633</v>
@@ -2163,7 +2163,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>50.048828125</v>
+        <v>50.0488166809082</v>
       </c>
       <c r="C77" t="n">
         <v>64.94999694824219</v>
@@ -2192,7 +2192,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>43.99981307983398</v>
+        <v>43.99980545043945</v>
       </c>
       <c r="C78" t="n">
         <v>57.09999847412109</v>
@@ -2221,7 +2221,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>46.30382537841797</v>
+        <v>46.3038330078125</v>
       </c>
       <c r="C79" t="n">
         <v>60.09000015258789</v>
@@ -2250,7 +2250,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>46.46564865112305</v>
+        <v>46.46566009521484</v>
       </c>
       <c r="C80" t="n">
         <v>60.29999923706055</v>
@@ -2308,7 +2308,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>53.96334457397461</v>
+        <v>53.96334838867188</v>
       </c>
       <c r="C82" t="n">
         <v>70.02999877929688</v>
@@ -2337,7 +2337,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>52.54904937744141</v>
+        <v>52.54905700683594</v>
       </c>
       <c r="C83" t="n">
         <v>67.41000366210938</v>
@@ -2366,7 +2366,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>52.94661712646484</v>
+        <v>52.94660186767578</v>
       </c>
       <c r="C84" t="n">
         <v>67.91999816894531</v>
@@ -2395,7 +2395,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>51.83966445922852</v>
+        <v>51.83968353271484</v>
       </c>
       <c r="C85" t="n">
         <v>66.5</v>
@@ -2424,7 +2424,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>56.04140853881836</v>
+        <v>56.04139709472656</v>
       </c>
       <c r="C86" t="n">
         <v>71.88999938964844</v>
@@ -2453,7 +2453,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>57.96687698364258</v>
+        <v>57.96685791015625</v>
       </c>
       <c r="C87" t="n">
         <v>74.36000061035156</v>
@@ -2482,7 +2482,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>59.22195434570312</v>
+        <v>59.2219352722168</v>
       </c>
       <c r="C88" t="n">
         <v>75.97000122070312</v>
@@ -2511,7 +2511,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>64.16804504394531</v>
+        <v>64.16806030273438</v>
       </c>
       <c r="C89" t="n">
         <v>81.44000244140625</v>
@@ -2569,7 +2569,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>56.6985969543457</v>
+        <v>56.69858932495117</v>
       </c>
       <c r="C91" t="n">
         <v>71.95999908447266</v>
@@ -2598,7 +2598,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>58.15625381469727</v>
+        <v>58.15624618530273</v>
       </c>
       <c r="C92" t="n">
         <v>73.80999755859375</v>
@@ -2627,7 +2627,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>56.92708206176758</v>
+        <v>56.92708587646484</v>
       </c>
       <c r="C93" t="n">
         <v>72.25</v>
@@ -2656,7 +2656,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>58.02230453491211</v>
+        <v>58.02228546142578</v>
       </c>
       <c r="C94" t="n">
         <v>73.63999938964844</v>
@@ -2685,7 +2685,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>58.67963409423828</v>
+        <v>58.67964172363281</v>
       </c>
       <c r="C95" t="n">
         <v>73.5</v>
@@ -2772,7 +2772,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>63.7731819152832</v>
+        <v>63.77318572998047</v>
       </c>
       <c r="C98" t="n">
         <v>79.87999725341797</v>
@@ -2801,7 +2801,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>66.54350280761719</v>
+        <v>66.54351043701172</v>
       </c>
       <c r="C99" t="n">
         <v>83.34999847412109</v>
@@ -2859,7 +2859,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>64.81455993652344</v>
+        <v>64.81456756591797</v>
       </c>
       <c r="C101" t="n">
         <v>80.22000122070312</v>
@@ -2888,7 +2888,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>65.80834197998047</v>
+        <v>65.808349609375</v>
       </c>
       <c r="C102" t="n">
         <v>81.44999694824219</v>
@@ -2917,7 +2917,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>65.31549072265625</v>
+        <v>65.31550598144531</v>
       </c>
       <c r="C103" t="n">
         <v>80.83999633789062</v>
@@ -2946,7 +2946,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>64.05508422851562</v>
+        <v>64.05506134033203</v>
       </c>
       <c r="C104" t="n">
         <v>79.27999877929688</v>
@@ -2975,7 +2975,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>65.49327087402344</v>
+        <v>65.49325561523438</v>
       </c>
       <c r="C105" t="n">
         <v>81.05999755859375</v>
@@ -3004,7 +3004,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>65.70331573486328</v>
+        <v>65.70332336425781</v>
       </c>
       <c r="C106" t="n">
         <v>81.31999969482422</v>
@@ -3062,7 +3062,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>70.69790649414062</v>
+        <v>70.69793701171875</v>
       </c>
       <c r="C108" t="n">
         <v>86.33000183105469</v>
@@ -3091,7 +3091,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>73.13831329345703</v>
+        <v>73.13832855224609</v>
       </c>
       <c r="C109" t="n">
         <v>89.30999755859375</v>
@@ -3120,7 +3120,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>68.81437683105469</v>
+        <v>68.81439971923828</v>
       </c>
       <c r="C110" t="n">
         <v>84.02999877929688</v>
@@ -3149,7 +3149,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>73.72792816162109</v>
+        <v>73.72793579101562</v>
       </c>
       <c r="C111" t="n">
         <v>90.02999877929688</v>
@@ -3178,7 +3178,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>76.72522735595703</v>
+        <v>76.72520446777344</v>
       </c>
       <c r="C112" t="n">
         <v>93.69000244140625</v>
@@ -3236,7 +3236,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>79.49083709716797</v>
+        <v>79.49086761474609</v>
       </c>
       <c r="C114" t="n">
         <v>96.04000091552734</v>
@@ -3265,7 +3265,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>80.10335540771484</v>
+        <v>80.10336303710938</v>
       </c>
       <c r="C115" t="n">
         <v>96.77999877929688</v>
@@ -3294,7 +3294,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>85.34259796142578</v>
+        <v>85.34261322021484</v>
       </c>
       <c r="C116" t="n">
         <v>103.1100006103516</v>
@@ -3323,7 +3323,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>78.02587890625</v>
+        <v>78.02586364746094</v>
       </c>
       <c r="C117" t="n">
         <v>94.26999664306641</v>
@@ -3352,7 +3352,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>81.32833099365234</v>
+        <v>81.32833862304688</v>
       </c>
       <c r="C118" t="n">
         <v>98.26000213623047</v>
@@ -3381,7 +3381,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>89.68115234375</v>
+        <v>89.68116760253906</v>
       </c>
       <c r="C119" t="n">
         <v>107.1999969482422</v>
@@ -3439,7 +3439,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>87.42239379882812</v>
+        <v>87.42238616943359</v>
       </c>
       <c r="C121" t="n">
         <v>104.5</v>
@@ -3468,7 +3468,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>88.29242706298828</v>
+        <v>88.29245758056641</v>
       </c>
       <c r="C122" t="n">
         <v>105.5400009155273</v>
@@ -3497,7 +3497,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>83.87532806396484</v>
+        <v>83.87532043457031</v>
       </c>
       <c r="C123" t="n">
         <v>100.2600021362305</v>
@@ -3526,7 +3526,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>96.54109191894531</v>
+        <v>96.54110717773438</v>
       </c>
       <c r="C124" t="n">
         <v>115.4000015258789</v>
@@ -3555,7 +3555,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>95.38361358642578</v>
+        <v>95.38360595703125</v>
       </c>
       <c r="C125" t="n">
         <v>112.9199981689453</v>
@@ -3613,7 +3613,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>95.69615936279297</v>
+        <v>95.69613647460938</v>
       </c>
       <c r="C127" t="n">
         <v>113.2900009155273</v>
@@ -3642,7 +3642,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>95.29070281982422</v>
+        <v>95.29068756103516</v>
       </c>
       <c r="C128" t="n">
         <v>112.8099975585938</v>
@@ -3671,7 +3671,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>97.14057922363281</v>
+        <v>97.14057159423828</v>
       </c>
       <c r="C129" t="n">
         <v>115</v>
@@ -3700,7 +3700,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>103.1970901489258</v>
+        <v>103.1970977783203</v>
       </c>
       <c r="C130" t="n">
         <v>122.1699981689453</v>
@@ -3787,7 +3787,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>99.96900177001953</v>
+        <v>99.96898651123047</v>
       </c>
       <c r="C133" t="n">
         <v>117.129997253418</v>
@@ -3816,7 +3816,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>97.18663024902344</v>
+        <v>97.18663787841797</v>
       </c>
       <c r="C134" t="n">
         <v>113.870002746582</v>
@@ -3845,7 +3845,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>104.5522384643555</v>
+        <v>104.5522308349609</v>
       </c>
       <c r="C135" t="n">
         <v>122.5</v>
@@ -3874,7 +3874,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>102.3161010742188</v>
+        <v>102.3160934448242</v>
       </c>
       <c r="C136" t="n">
         <v>119.879997253418</v>
@@ -3903,7 +3903,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>104.6021270751953</v>
+        <v>104.6021041870117</v>
       </c>
       <c r="C137" t="n">
         <v>121.3000030517578</v>
@@ -3932,7 +3932,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>107.3357696533203</v>
+        <v>107.3357543945312</v>
       </c>
       <c r="C138" t="n">
         <v>124.4700012207031</v>
@@ -3961,7 +3961,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>106.6545181274414</v>
+        <v>106.6544876098633</v>
       </c>
       <c r="C139" t="n">
         <v>123.6800003051758</v>
@@ -3990,7 +3990,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>111.0869522094727</v>
+        <v>111.0869445800781</v>
       </c>
       <c r="C140" t="n">
         <v>128.8200073242188</v>
@@ -4048,7 +4048,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>116.4765777587891</v>
+        <v>116.4765853881836</v>
       </c>
       <c r="C142" t="n">
         <v>135.0700073242188</v>
@@ -4077,7 +4077,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>123.9520721435547</v>
+        <v>123.9520645141602</v>
       </c>
       <c r="C143" t="n">
         <v>142.3600006103516</v>
@@ -4106,7 +4106,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>128.8715057373047</v>
+        <v>128.8714904785156</v>
       </c>
       <c r="C144" t="n">
         <v>148.0099945068359</v>
@@ -4193,7 +4193,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>140.1905059814453</v>
+        <v>140.1904754638672</v>
       </c>
       <c r="C147" t="n">
         <v>161.0099945068359</v>
@@ -4222,7 +4222,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>133.6515502929688</v>
+        <v>133.6515808105469</v>
       </c>
       <c r="C148" t="n">
         <v>153.5</v>
@@ -4280,7 +4280,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>136.7985229492188</v>
+        <v>136.7985687255859</v>
       </c>
       <c r="C150" t="n">
         <v>155.7400054931641</v>
@@ -4309,7 +4309,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>143.6938323974609</v>
+        <v>143.6937561035156</v>
       </c>
       <c r="C151" t="n">
         <v>163.5899963378906</v>
@@ -4338,7 +4338,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>139.9519195556641</v>
+        <v>139.9519500732422</v>
       </c>
       <c r="C152" t="n">
         <v>159.3300018310547</v>
@@ -4367,7 +4367,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>148.5072937011719</v>
+        <v>148.50732421875</v>
       </c>
       <c r="C153" t="n">
         <v>169.0700073242188</v>
@@ -4396,7 +4396,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>149.4998779296875</v>
+        <v>149.4999084472656</v>
       </c>
       <c r="C154" t="n">
         <v>170.1999969482422</v>
@@ -4425,7 +4425,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>139.7152862548828</v>
+        <v>139.7152557373047</v>
       </c>
       <c r="C155" t="n">
         <v>157.6199951171875</v>
@@ -4454,7 +4454,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>145.8315124511719</v>
+        <v>145.8315277099609</v>
       </c>
       <c r="C156" t="n">
         <v>164.5200042724609</v>
@@ -4483,7 +4483,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>124.9920883178711</v>
+        <v>124.992073059082</v>
       </c>
       <c r="C157" t="n">
         <v>141.0099945068359</v>
@@ -4512,7 +4512,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>136.1076354980469</v>
+        <v>136.1076202392578</v>
       </c>
       <c r="C158" t="n">
         <v>153.5500030517578</v>
@@ -4541,7 +4541,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>143.0481719970703</v>
+        <v>143.0481872558594</v>
       </c>
       <c r="C159" t="n">
         <v>161.3800048828125</v>
@@ -4599,7 +4599,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>163.2608795166016</v>
+        <v>163.2608642578125</v>
       </c>
       <c r="C161" t="n">
         <v>182.6699981689453</v>
@@ -4628,7 +4628,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>159.1496429443359</v>
+        <v>159.1497039794922</v>
       </c>
       <c r="C162" t="n">
         <v>178.0700073242188</v>
@@ -4657,7 +4657,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>165.1377868652344</v>
+        <v>165.1377563476562</v>
       </c>
       <c r="C163" t="n">
         <v>184.7700042724609</v>
@@ -4715,7 +4715,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>177.1139526367188</v>
+        <v>177.114013671875</v>
       </c>
       <c r="C165" t="n">
         <v>198.1699981689453</v>
@@ -4773,7 +4773,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>166.4307403564453</v>
+        <v>166.4306793212891</v>
       </c>
       <c r="C167" t="n">
         <v>185.4199981689453</v>
@@ -4831,7 +4831,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>189.0050659179688</v>
+        <v>189.0050354003906</v>
       </c>
       <c r="C169" t="n">
         <v>210.5700073242188</v>
@@ -4860,7 +4860,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>184.9060974121094</v>
+        <v>184.9060516357422</v>
       </c>
       <c r="C170" t="n">
         <v>205.2100067138672</v>
@@ -4947,7 +4947,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>167.6198272705078</v>
+        <v>167.6198120117188</v>
       </c>
       <c r="C173" t="n">
         <v>185.1900024414062</v>
@@ -4976,7 +4976,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>182.4910125732422</v>
+        <v>182.4909973144531</v>
       </c>
       <c r="C174" t="n">
         <v>201.6199951171875</v>
@@ -5034,7 +5034,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>204.1990966796875</v>
+        <v>204.1990356445312</v>
       </c>
       <c r="C176" t="n">
         <v>224.7799987792969</v>
@@ -5063,7 +5063,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>217.9619293212891</v>
+        <v>217.9619140625</v>
       </c>
       <c r="C177" t="n">
         <v>239.9299926757812</v>
@@ -5121,7 +5121,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>197.8212127685547</v>
+        <v>197.8212432861328</v>
       </c>
       <c r="C179" t="n">
         <v>216.9100036621094</v>
@@ -5179,7 +5179,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>238.2226715087891</v>
+        <v>238.2227020263672</v>
       </c>
       <c r="C181" t="n">
         <v>261.2099914550781</v>
@@ -5208,7 +5208,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>221.3842468261719</v>
+        <v>221.3841857910156</v>
       </c>
       <c r="C182" t="n">
         <v>241.9199981689453</v>
@@ -5237,7 +5237,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>229.6019592285156</v>
+        <v>229.6019287109375</v>
       </c>
       <c r="C183" t="n">
         <v>250.8999938964844</v>
@@ -5266,7 +5266,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>252.7999725341797</v>
+        <v>252.800048828125</v>
       </c>
       <c r="C184" t="n">
         <v>276.25</v>
@@ -5353,7 +5353,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>270.6011352539062</v>
+        <v>270.6011962890625</v>
       </c>
       <c r="C187" t="n">
         <v>294.7900085449219</v>
@@ -5411,7 +5411,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>309.8158569335938</v>
+        <v>309.8157653808594</v>
       </c>
       <c r="C189" t="n">
         <v>336.5599975585938</v>
@@ -5440,7 +5440,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>294.4981079101562</v>
+        <v>294.4980773925781</v>
       </c>
       <c r="C190" t="n">
         <v>319.9200134277344</v>
@@ -5469,7 +5469,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>331.2599487304688</v>
+        <v>331.2599182128906</v>
       </c>
       <c r="C191" t="n">
         <v>358.7900085449219</v>
@@ -5498,7 +5498,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>329.9765319824219</v>
+        <v>329.9765930175781</v>
       </c>
       <c r="C192" t="n">
         <v>357.3999938964844</v>
@@ -5527,7 +5527,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>382.7414245605469</v>
+        <v>382.7413635253906</v>
       </c>
       <c r="C193" t="n">
         <v>414.5499877929688</v>
@@ -5614,7 +5614,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>312.1614685058594</v>
+        <v>312.161376953125</v>
       </c>
       <c r="C196" t="n">
         <v>337.2300109863281</v>
@@ -5643,7 +5643,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>278.860107421875</v>
+        <v>278.8600769042969</v>
       </c>
       <c r="C197" t="n">
         <v>300.3599853515625</v>
@@ -5759,7 +5759,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>268.7645568847656</v>
+        <v>268.7645263671875</v>
       </c>
       <c r="C201" t="n">
         <v>288.4599914550781</v>
@@ -5788,7 +5788,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>239.7320709228516</v>
+        <v>239.7320556640625</v>
       </c>
       <c r="C202" t="n">
         <v>257.2999877929688</v>
@@ -5875,7 +5875,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>249.7262878417969</v>
+        <v>249.7263031005859</v>
       </c>
       <c r="C205" t="n">
         <v>266.8399963378906</v>
@@ -5904,7 +5904,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>262.2213745117188</v>
+        <v>262.2214050292969</v>
       </c>
       <c r="C206" t="n">
         <v>279.0499877929688</v>
@@ -5933,7 +5933,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>249.5355529785156</v>
+        <v>249.5355834960938</v>
       </c>
       <c r="C207" t="n">
         <v>265.5499877929688</v>
@@ -5962,7 +5962,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>268.5737915039062</v>
+        <v>268.5737609863281</v>
       </c>
       <c r="C208" t="n">
         <v>285.8099975585938</v>
@@ -5991,7 +5991,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>264.4209289550781</v>
+        <v>264.4209594726562</v>
       </c>
       <c r="C209" t="n">
         <v>280.2900085449219</v>
@@ -6049,7 +6049,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>291.1092224121094</v>
+        <v>291.1092529296875</v>
       </c>
       <c r="C211" t="n">
         <v>308.5799865722656</v>
@@ -6078,7 +6078,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>299.5224914550781</v>
+        <v>299.5224609375</v>
       </c>
       <c r="C212" t="n">
         <v>316.3500061035156</v>
@@ -6107,7 +6107,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>306.5477600097656</v>
+        <v>306.5477905273438</v>
       </c>
       <c r="C213" t="n">
         <v>323.7699890136719</v>
@@ -6136,7 +6136,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>290.7739562988281</v>
+        <v>290.77392578125</v>
       </c>
       <c r="C214" t="n">
         <v>307.1099853515625</v>
@@ -6165,7 +6165,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>282.4536437988281</v>
+        <v>282.45361328125</v>
       </c>
       <c r="C215" t="n">
         <v>297.0899963378906</v>
@@ -6194,7 +6194,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>316.7275695800781</v>
+        <v>316.7275390625</v>
       </c>
       <c r="C216" t="n">
         <v>333.1400146484375</v>
@@ -6223,7 +6223,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>333.6221008300781</v>
+        <v>333.6221313476562</v>
       </c>
       <c r="C217" t="n">
         <v>350.9100036621094</v>
@@ -6252,7 +6252,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>347.2164001464844</v>
+        <v>347.2164306640625</v>
       </c>
       <c r="C218" t="n">
         <v>363.8800048828125</v>
@@ -6281,7 +6281,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>357.6172180175781</v>
+        <v>357.6172485351562</v>
       </c>
       <c r="C219" t="n">
         <v>374.7799987792969</v>
@@ -6310,7 +6310,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>330.7372741699219</v>
+        <v>330.7372436523438</v>
       </c>
       <c r="C220" t="n">
         <v>346.6099853515625</v>
@@ -6339,7 +6339,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>288.2418518066406</v>
+        <v>288.2418212890625</v>
       </c>
       <c r="C221" t="n">
         <v>300.9100036621094</v>
@@ -6368,7 +6368,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>270.4057312011719</v>
+        <v>270.40576171875</v>
       </c>
       <c r="C222" t="n">
         <v>282.2900085449219</v>
@@ -6426,7 +6426,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>318.0899963378906</v>
+        <v>318.0899658203125</v>
       </c>
       <c r="C224" t="n">
         <v>330.6199951171875</v>
@@ -6455,7 +6455,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>328.9906311035156</v>
+        <v>328.9906005859375</v>
       </c>
       <c r="C225" t="n">
         <v>341.9500122070312</v>
@@ -6484,7 +6484,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>340.0836181640625</v>
+        <v>340.0835876464844</v>
       </c>
       <c r="C226" t="n">
         <v>353.4800109863281</v>
@@ -6513,7 +6513,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>333.1022033691406</v>
+        <v>333.1021728515625</v>
       </c>
       <c r="C227" t="n">
         <v>344.8200073242188</v>
@@ -6571,7 +6571,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>339.8353271484375</v>
+        <v>339.8352966308594</v>
       </c>
       <c r="C229" t="n">
         <v>351.7900085449219</v>
@@ -6629,7 +6629,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>338.0878601074219</v>
+        <v>338.0878295898438</v>
       </c>
       <c r="C231" t="n">
         <v>348.5</v>
@@ -6658,7 +6658,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>302.7171630859375</v>
+        <v>302.7171936035156</v>
       </c>
       <c r="C232" t="n">
         <v>312.0400085449219</v>
@@ -6716,7 +6716,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>308.8784484863281</v>
+        <v>308.8784790039062</v>
       </c>
       <c r="C234" t="n">
         <v>316.8200073242188</v>
@@ -6745,7 +6745,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>291.3978881835938</v>
+        <v>291.3979187011719</v>
       </c>
       <c r="C235" t="n">
         <v>298.8900146484375</v>
@@ -6803,7 +6803,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>254.7210845947266</v>
+        <v>254.7210693359375</v>
       </c>
       <c r="C237" t="n">
         <v>259.9700012207031</v>
@@ -6890,7 +6890,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>244.952392578125</v>
+        <v>244.9523773193359</v>
       </c>
       <c r="C240" t="n">
         <v>250</v>
@@ -6919,7 +6919,7 @@
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>262.8829040527344</v>
+        <v>262.8828735351562</v>
       </c>
       <c r="C241" t="n">
         <v>268.2999877929688</v>
@@ -6977,7 +6977,7 @@
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>204.505859375</v>
+        <v>204.5058441162109</v>
       </c>
       <c r="C243" t="n">
         <v>208.7200012207031</v>
@@ -7006,7 +7006,7 @@
         <v>46112</v>
       </c>
       <c r="B244" t="n">
-        <v>194.2864379882812</v>
+        <v>194.2864227294922</v>
       </c>
       <c r="C244" t="n">
         <v>198.2899932861328</v>
